--- a/Cases/PS Report Painter CJE2 S_ALR_.xlsx
+++ b/Cases/PS Report Painter CJE2 S_ALR_.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70023796\Desktop\Project\Main_Link\RepoGit\Additional\Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC407579-42C8-4B2C-9401-4D62F10CED2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285543CB-B083-42C4-9762-2ED19AF02A29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3017" yWindow="926" windowWidth="12052" windowHeight="10697" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Cách lọc theo CE cho cột Actual của báo cáo PS S_ALR_87013558 theo Valuation Category (Hoặc xem theo báo cáo S_ALR_87013542 sẽ nhanh hơn chỉ cần tạo Group CE lưu vào variant dùng luôn nhưng sẽ ko có budget):</t>
   </si>
@@ -64,6 +64,33 @@
   </si>
   <si>
     <t>CJEV tạo Variable cho Project Report cho Value Cat với Field Name ACPOS và Replacement Type Entry + Optional</t>
+  </si>
+  <si>
+    <t>Report Painter</t>
+  </si>
+  <si>
+    <t>Chỉnh layout độ dài Lead Column</t>
+  </si>
+  <si>
+    <t>Chọn 1 dòng của cột Lead rồi Settings/Characteristic Display</t>
+  </si>
+  <si>
+    <t>Bật tắt cột hiển thị</t>
+  </si>
+  <si>
+    <t>Chọn cột cần bật tắt rồi Edit/Columns/On Off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lưu Layout </t>
+  </si>
+  <si>
+    <t>Chọn Report/Save Definition</t>
+  </si>
+  <si>
+    <t>Export báo cáo</t>
+  </si>
+  <si>
+    <t>Chạy dạng Graphical rồi export to HTML, mở file %2 bằng Excel</t>
   </si>
 </sst>
 </file>
@@ -392,72 +419,109 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
